--- a/food_beverage_order_forms/029_pizza_toppings_selection_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/029_pizza_toppings_selection_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'topping_1',_'label':_'cheese',_'type':_'option'}</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'topping_1', 'label': 'Cheese', 'type': 'option'}</t>
+          <t>Cheese</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'topping_2',_'label':_'pepperoni',_'type':_'option'}</t>
+          <t>pepperoni</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'topping_2', 'label': 'Pepperoni', 'type': 'option'}</t>
+          <t>Pepperoni</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'topping_3',_'label':_'mushroom',_'type':_'option'}</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'topping_3', 'label': 'Mushroom', 'type': 'option'}</t>
+          <t>Mushroom</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'topping_4',_'label':_'onions',_'type':_'option'}</t>
+          <t>onions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'topping_4', 'label': 'Onions', 'type': 'option'}</t>
+          <t>Onions</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'topping_5',_'label':_'bacon',_'type':_'option'}</t>
+          <t>bacon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'topping_5', 'label': 'Bacon', 'type': 'option'}</t>
+          <t>Bacon</t>
         </is>
       </c>
     </row>
